--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1733-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1733-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E0DF823-E2C8-40A9-A220-982756DD304E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68934494-8936-493C-A879-A3F400CB3337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{DBEB3C3F-6755-4A29-BEE8-1E8698A37A2D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{98443D7D-787D-4424-AE24-755D86DA1A50}"/>
   </bookViews>
   <sheets>
     <sheet name="1733-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1484,27 +1484,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAD42A66-5C0C-409B-9678-BFBD6D6BF0C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D26476A-5ABF-4FA1-AF7F-C4E9930C4AA0}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="8" width="6.25" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1538,7 +1537,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1574,7 +1573,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1626,7 +1625,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1694,7 +1693,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1766,7 +1765,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1838,7 +1837,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1910,7 +1909,7 @@
         <v>5.67</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1982,7 +1981,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2054,7 +2053,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2126,7 +2125,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2198,7 +2197,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2270,7 +2269,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2342,7 +2341,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2414,7 +2413,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2486,7 +2485,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2558,7 +2557,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2630,7 +2629,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2702,7 +2701,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2774,7 +2773,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2846,7 +2845,7 @@
         <v>5.78</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2918,7 +2917,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2990,7 +2989,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3062,7 +3061,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3134,7 +3133,7 @@
         <v>9.11</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3206,7 +3205,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3278,7 +3277,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3350,7 +3349,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3422,7 +3421,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3494,7 +3493,7 @@
         <v>7.56</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>1999</v>
       </c>
@@ -3566,7 +3565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1998</v>
       </c>
@@ -3638,7 +3637,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1997</v>
       </c>
@@ -3710,7 +3709,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="34" t="s">
         <v>53</v>
       </c>
